--- a/MC2020_E25.xlsx
+++ b/MC2020_E25.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\anjushiya\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS-2024-2\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D58C033D-BDB8-4569-90D3-4CB7BBF345AE}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06516830-6FBB-4470-99CE-9AEEC2FCAC8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-110" yWindow="-110" windowWidth="19420" windowHeight="10420" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -1418,7 +1418,7 @@
     <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="34">
+  <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1449,41 +1449,41 @@
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="11" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
     <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="8" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="11" applyFont="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="10" fillId="0" borderId="0" xfId="11" applyFont="1" applyAlignment="1">
       <alignment vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="10" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
@@ -1505,6 +1505,9 @@
       <alignment horizontal="left" vertical="center"/>
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
   </cellXfs>
   <cellStyles count="12">
     <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
@@ -1792,13 +1795,13 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:H238"/>
-  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.5"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
-    <col min="1" max="1" width="14.54296875" customWidth="1"/>
+    <col min="1" max="1" width="14.5703125" customWidth="1"/>
     <col min="2" max="2" width="39" customWidth="1"/>
-    <col min="3" max="6" width="13.54296875" customWidth="1"/>
-    <col min="7" max="7" width="15.54296875" customWidth="1"/>
-    <col min="8" max="8" width="15.54296875" style="1" customWidth="1"/>
+    <col min="3" max="6" width="13.5703125" customWidth="1"/>
+    <col min="7" max="7" width="15.5703125" customWidth="1"/>
+    <col min="8" max="8" width="15.5703125" style="1" customWidth="1"/>
     <col min="14" max="14" width="9" customWidth="1"/>
   </cols>
   <sheetData>
@@ -1835,7 +1838,7 @@
       <c r="B2" s="27" t="s">
         <v>9</v>
       </c>
-      <c r="C2" s="10" t="s">
+      <c r="C2" s="34" t="s">
         <v>383</v>
       </c>
       <c r="D2" s="9">
@@ -5749,12 +5752,9 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5902,24 +5902,15 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -5933,4 +5924,16 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
 </file>
--- a/MC2020_E25.xlsx
+++ b/MC2020_E25.xlsx
@@ -1,21 +1,20 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="30228"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" mc:Ignorable="x15">
+  <fileVersion appName="xl" lastEdited="6" lowestEdited="7" rupBuild="14420"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\IDS-2024-2\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{06516830-6FBB-4470-99CE-9AEEC2FCAC8F}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="152511"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -1221,9 +1220,9 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <numFmts count="1">
-    <numFmt numFmtId="164" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
+    <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
   <fonts count="13">
     <font>
@@ -1415,25 +1414,25 @@
     <xf numFmtId="0" fontId="4" fillId="2" borderId="0" applyNumberFormat="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
-    <xf numFmtId="164" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
+    <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="35">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
+    <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
-    <xf numFmtId="164" fontId="2" fillId="9" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="2" fillId="9" borderId="1" xfId="10" applyFont="1" applyFill="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="8" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="164" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="8" fillId="0" borderId="1" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
@@ -1467,7 +1466,7 @@
     <xf numFmtId="2" fontId="8" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
-    <xf numFmtId="164" fontId="12" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="43" fontId="12" fillId="0" borderId="0" xfId="10" applyFont="1" applyBorder="1"/>
     <xf numFmtId="2" fontId="9" fillId="0" borderId="0" xfId="0" applyNumberFormat="1" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
@@ -1510,18 +1509,18 @@
     </xf>
   </cellXfs>
   <cellStyles count="12">
-    <cellStyle name="60% - Accent1 2" xfId="1" xr:uid="{00000000-0005-0000-0000-000000000000}"/>
-    <cellStyle name="60% - Accent2 2" xfId="2" xr:uid="{00000000-0005-0000-0000-000001000000}"/>
-    <cellStyle name="60% - Accent3 2" xfId="3" xr:uid="{00000000-0005-0000-0000-000002000000}"/>
-    <cellStyle name="60% - Accent4 2" xfId="4" xr:uid="{00000000-0005-0000-0000-000003000000}"/>
-    <cellStyle name="60% - Accent5 2" xfId="5" xr:uid="{00000000-0005-0000-0000-000004000000}"/>
-    <cellStyle name="60% - Accent6 2" xfId="6" xr:uid="{00000000-0005-0000-0000-000005000000}"/>
+    <cellStyle name="60% - Accent1 2" xfId="1"/>
+    <cellStyle name="60% - Accent2 2" xfId="2"/>
+    <cellStyle name="60% - Accent3 2" xfId="3"/>
+    <cellStyle name="60% - Accent4 2" xfId="4"/>
+    <cellStyle name="60% - Accent5 2" xfId="5"/>
+    <cellStyle name="60% - Accent6 2" xfId="6"/>
     <cellStyle name="Comma" xfId="10" builtinId="3"/>
-    <cellStyle name="Neutral 2" xfId="7" xr:uid="{00000000-0005-0000-0000-000007000000}"/>
+    <cellStyle name="Neutral 2" xfId="7"/>
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
-    <cellStyle name="Normal 2" xfId="8" xr:uid="{00000000-0005-0000-0000-000009000000}"/>
-    <cellStyle name="Normal 3" xfId="11" xr:uid="{CC3ED8B0-E380-41DE-99A4-8D57C518D190}"/>
-    <cellStyle name="Title 2" xfId="9" xr:uid="{00000000-0005-0000-0000-00000A000000}"/>
+    <cellStyle name="Normal 2" xfId="8"/>
+    <cellStyle name="Normal 3" xfId="11"/>
+    <cellStyle name="Title 2" xfId="9"/>
   </cellStyles>
   <dxfs count="0"/>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium2" defaultPivotStyle="PivotStyleLight16"/>
@@ -1793,7 +1792,7 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
   <dimension ref="A1:H238"/>
   <sheetFormatPr defaultColWidth="9" defaultRowHeight="15"/>
   <cols>
@@ -1802,7 +1801,6 @@
     <col min="3" max="6" width="13.5703125" customWidth="1"/>
     <col min="7" max="7" width="15.5703125" customWidth="1"/>
     <col min="8" max="8" width="15.5703125" style="1" customWidth="1"/>
-    <col min="14" max="14" width="9" customWidth="1"/>
   </cols>
   <sheetData>
     <row r="1" spans="1:8" ht="18.75" customHeight="1">
@@ -1847,7 +1845,9 @@
       <c r="E2" s="5"/>
       <c r="F2" s="5"/>
       <c r="G2" s="10"/>
-      <c r="H2" s="8"/>
+      <c r="H2" s="8">
+        <v>64.285714299999995</v>
+      </c>
     </row>
     <row r="3" spans="1:8">
       <c r="A3" s="11" t="s">
@@ -1865,7 +1865,9 @@
       <c r="E3" s="5"/>
       <c r="F3" s="5"/>
       <c r="G3" s="10"/>
-      <c r="H3" s="8"/>
+      <c r="H3" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="4" spans="1:8">
       <c r="A4" s="11" t="s">
@@ -1883,7 +1885,9 @@
       <c r="E4" s="5"/>
       <c r="F4" s="5"/>
       <c r="G4" s="10"/>
-      <c r="H4" s="8"/>
+      <c r="H4" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="5" spans="1:8">
       <c r="A5" s="11" t="s">
@@ -1901,7 +1905,9 @@
       <c r="E5" s="5"/>
       <c r="F5" s="5"/>
       <c r="G5" s="10"/>
-      <c r="H5" s="8"/>
+      <c r="H5" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="6" spans="1:8">
       <c r="A6" s="12" t="s">
@@ -1919,7 +1925,9 @@
       <c r="E6" s="5"/>
       <c r="F6" s="5"/>
       <c r="G6" s="10"/>
-      <c r="H6" s="8"/>
+      <c r="H6" s="8">
+        <v>28.571428599999997</v>
+      </c>
     </row>
     <row r="7" spans="1:8">
       <c r="A7" s="12" t="s">
@@ -1937,7 +1945,9 @@
       <c r="E7" s="5"/>
       <c r="F7" s="5"/>
       <c r="G7" s="10"/>
-      <c r="H7" s="8"/>
+      <c r="H7" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="8" spans="1:8">
       <c r="A8" s="12" t="s">
@@ -1955,7 +1965,9 @@
       <c r="E8" s="5"/>
       <c r="F8" s="5"/>
       <c r="G8" s="10"/>
-      <c r="H8" s="8"/>
+      <c r="H8" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="9" spans="1:8">
       <c r="A9" s="12" t="s">
@@ -1973,7 +1985,9 @@
       <c r="E9" s="5"/>
       <c r="F9" s="5"/>
       <c r="G9" s="10"/>
-      <c r="H9" s="8"/>
+      <c r="H9" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="10" spans="1:8">
       <c r="A10" s="12" t="s">
@@ -1991,7 +2005,9 @@
       <c r="E10" s="5"/>
       <c r="F10" s="5"/>
       <c r="G10" s="10"/>
-      <c r="H10" s="8"/>
+      <c r="H10" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="11" spans="1:8">
       <c r="A11" s="12" t="s">
@@ -2009,7 +2025,9 @@
       <c r="E11" s="5"/>
       <c r="F11" s="5"/>
       <c r="G11" s="10"/>
-      <c r="H11" s="8"/>
+      <c r="H11" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="12" spans="1:8">
       <c r="A12" s="12" t="s">
@@ -2027,7 +2045,9 @@
       <c r="E12" s="5"/>
       <c r="F12" s="5"/>
       <c r="G12" s="10"/>
-      <c r="H12" s="8"/>
+      <c r="H12" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="13" spans="1:8">
       <c r="A13" s="12" t="s">
@@ -2045,7 +2065,9 @@
       <c r="E13" s="5"/>
       <c r="F13" s="5"/>
       <c r="G13" s="10"/>
-      <c r="H13" s="8"/>
+      <c r="H13" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="14" spans="1:8">
       <c r="A14" s="12" t="s">
@@ -2063,7 +2085,9 @@
       <c r="E14" s="5"/>
       <c r="F14" s="5"/>
       <c r="G14" s="10"/>
-      <c r="H14" s="8"/>
+      <c r="H14" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="15" spans="1:8">
       <c r="A15" s="12" t="s">
@@ -2081,7 +2105,9 @@
       <c r="E15" s="5"/>
       <c r="F15" s="5"/>
       <c r="G15" s="10"/>
-      <c r="H15" s="8"/>
+      <c r="H15" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="16" spans="1:8">
       <c r="A16" s="12" t="s">
@@ -2099,7 +2125,9 @@
       <c r="E16" s="5"/>
       <c r="F16" s="5"/>
       <c r="G16" s="10"/>
-      <c r="H16" s="8"/>
+      <c r="H16" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="17" spans="1:8">
       <c r="A17" s="12" t="s">
@@ -2117,7 +2145,9 @@
       <c r="E17" s="5"/>
       <c r="F17" s="5"/>
       <c r="G17" s="10"/>
-      <c r="H17" s="8"/>
+      <c r="H17" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="18" spans="1:8">
       <c r="A18" s="12" t="s">
@@ -2135,7 +2165,9 @@
       <c r="E18" s="5"/>
       <c r="F18" s="5"/>
       <c r="G18" s="10"/>
-      <c r="H18" s="8"/>
+      <c r="H18" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="19" spans="1:8">
       <c r="A19" s="12" t="s">
@@ -2153,7 +2185,9 @@
       <c r="E19" s="5"/>
       <c r="F19" s="5"/>
       <c r="G19" s="10"/>
-      <c r="H19" s="8"/>
+      <c r="H19" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="20" spans="1:8">
       <c r="A20" s="12" t="s">
@@ -2171,7 +2205,9 @@
       <c r="E20" s="5"/>
       <c r="F20" s="5"/>
       <c r="G20" s="10"/>
-      <c r="H20" s="8"/>
+      <c r="H20" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="21" spans="1:8">
       <c r="A21" s="12" t="s">
@@ -2189,7 +2225,9 @@
       <c r="E21" s="5"/>
       <c r="F21" s="5"/>
       <c r="G21" s="10"/>
-      <c r="H21" s="8"/>
+      <c r="H21" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="22" spans="1:8">
       <c r="A22" s="12" t="s">
@@ -2207,7 +2245,9 @@
       <c r="E22" s="5"/>
       <c r="F22" s="5"/>
       <c r="G22" s="10"/>
-      <c r="H22" s="8"/>
+      <c r="H22" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="23" spans="1:8">
       <c r="A23" s="12" t="s">
@@ -2225,7 +2265,9 @@
       <c r="E23" s="5"/>
       <c r="F23" s="5"/>
       <c r="G23" s="10"/>
-      <c r="H23" s="8"/>
+      <c r="H23" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="24" spans="1:8">
       <c r="A24" s="12" t="s">
@@ -2243,7 +2285,9 @@
       <c r="E24" s="5"/>
       <c r="F24" s="5"/>
       <c r="G24" s="10"/>
-      <c r="H24" s="8"/>
+      <c r="H24" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="25" spans="1:8">
       <c r="A25" s="12" t="s">
@@ -2261,7 +2305,9 @@
       <c r="E25" s="5"/>
       <c r="F25" s="5"/>
       <c r="G25" s="10"/>
-      <c r="H25" s="8"/>
+      <c r="H25" s="8">
+        <v>64.285714299999995</v>
+      </c>
     </row>
     <row r="26" spans="1:8">
       <c r="A26" s="12" t="s">
@@ -2279,7 +2325,9 @@
       <c r="E26" s="5"/>
       <c r="F26" s="5"/>
       <c r="G26" s="10"/>
-      <c r="H26" s="8"/>
+      <c r="H26" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="27" spans="1:8">
       <c r="A27" s="12" t="s">
@@ -2297,7 +2345,9 @@
       <c r="E27" s="5"/>
       <c r="F27" s="5"/>
       <c r="G27" s="10"/>
-      <c r="H27" s="8"/>
+      <c r="H27" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="28" spans="1:8">
       <c r="A28" s="12" t="s">
@@ -2315,7 +2365,9 @@
       <c r="E28" s="5"/>
       <c r="F28" s="5"/>
       <c r="G28" s="10"/>
-      <c r="H28" s="8"/>
+      <c r="H28" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="29" spans="1:8">
       <c r="A29" s="12" t="s">
@@ -2333,7 +2385,9 @@
       <c r="E29" s="5"/>
       <c r="F29" s="5"/>
       <c r="G29" s="10"/>
-      <c r="H29" s="8"/>
+      <c r="H29" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="30" spans="1:8">
       <c r="A30" s="12" t="s">
@@ -2351,7 +2405,9 @@
       <c r="E30" s="5"/>
       <c r="F30" s="5"/>
       <c r="G30" s="10"/>
-      <c r="H30" s="8"/>
+      <c r="H30" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="31" spans="1:8">
       <c r="A31" s="12" t="s">
@@ -2369,7 +2425,9 @@
       <c r="E31" s="5"/>
       <c r="F31" s="5"/>
       <c r="G31" s="10"/>
-      <c r="H31" s="8"/>
+      <c r="H31" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="32" spans="1:8">
       <c r="A32" s="12" t="s">
@@ -2387,7 +2445,9 @@
       <c r="E32" s="5"/>
       <c r="F32" s="5"/>
       <c r="G32" s="10"/>
-      <c r="H32" s="8"/>
+      <c r="H32" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="33" spans="1:8">
       <c r="A33" s="12" t="s">
@@ -2405,7 +2465,9 @@
       <c r="E33" s="5"/>
       <c r="F33" s="5"/>
       <c r="G33" s="10"/>
-      <c r="H33" s="8"/>
+      <c r="H33" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="34" spans="1:8">
       <c r="A34" s="12" t="s">
@@ -2423,7 +2485,9 @@
       <c r="E34" s="5"/>
       <c r="F34" s="5"/>
       <c r="G34" s="10"/>
-      <c r="H34" s="8"/>
+      <c r="H34" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="35" spans="1:8">
       <c r="A35" s="12" t="s">
@@ -2441,7 +2505,9 @@
       <c r="E35" s="5"/>
       <c r="F35" s="5"/>
       <c r="G35" s="10"/>
-      <c r="H35" s="8"/>
+      <c r="H35" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="36" spans="1:8">
       <c r="A36" s="12" t="s">
@@ -2459,7 +2525,9 @@
       <c r="E36" s="5"/>
       <c r="F36" s="5"/>
       <c r="G36" s="10"/>
-      <c r="H36" s="8"/>
+      <c r="H36" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="37" spans="1:8">
       <c r="A37" s="12" t="s">
@@ -2477,7 +2545,9 @@
       <c r="E37" s="5"/>
       <c r="F37" s="5"/>
       <c r="G37" s="10"/>
-      <c r="H37" s="8"/>
+      <c r="H37" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="38" spans="1:8">
       <c r="A38" s="12" t="s">
@@ -2495,7 +2565,9 @@
       <c r="E38" s="5"/>
       <c r="F38" s="5"/>
       <c r="G38" s="10"/>
-      <c r="H38" s="8"/>
+      <c r="H38" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="39" spans="1:8">
       <c r="A39" s="12" t="s">
@@ -2513,7 +2585,9 @@
       <c r="E39" s="5"/>
       <c r="F39" s="5"/>
       <c r="G39" s="10"/>
-      <c r="H39" s="8"/>
+      <c r="H39" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="40" spans="1:8">
       <c r="A40" s="12" t="s">
@@ -2531,7 +2605,9 @@
       <c r="E40" s="5"/>
       <c r="F40" s="5"/>
       <c r="G40" s="10"/>
-      <c r="H40" s="8"/>
+      <c r="H40" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="41" spans="1:8">
       <c r="A41" s="12" t="s">
@@ -2549,7 +2625,9 @@
       <c r="E41" s="5"/>
       <c r="F41" s="5"/>
       <c r="G41" s="10"/>
-      <c r="H41" s="8"/>
+      <c r="H41" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="42" spans="1:8">
       <c r="A42" s="12" t="s">
@@ -2567,7 +2645,9 @@
       <c r="E42" s="5"/>
       <c r="F42" s="5"/>
       <c r="G42" s="10"/>
-      <c r="H42" s="8"/>
+      <c r="H42" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="43" spans="1:8">
       <c r="A43" s="12" t="s">
@@ -2585,7 +2665,9 @@
       <c r="E43" s="5"/>
       <c r="F43" s="5"/>
       <c r="G43" s="10"/>
-      <c r="H43" s="8"/>
+      <c r="H43" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="44" spans="1:8">
       <c r="A44" s="12" t="s">
@@ -2603,7 +2685,9 @@
       <c r="E44" s="5"/>
       <c r="F44" s="5"/>
       <c r="G44" s="10"/>
-      <c r="H44" s="8"/>
+      <c r="H44" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="45" spans="1:8">
       <c r="A45" s="12" t="s">
@@ -2621,7 +2705,9 @@
       <c r="E45" s="5"/>
       <c r="F45" s="5"/>
       <c r="G45" s="10"/>
-      <c r="H45" s="8"/>
+      <c r="H45" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="46" spans="1:8">
       <c r="A46" s="12" t="s">
@@ -2639,7 +2725,9 @@
       <c r="E46" s="5"/>
       <c r="F46" s="5"/>
       <c r="G46" s="10"/>
-      <c r="H46" s="8"/>
+      <c r="H46" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="47" spans="1:8">
       <c r="A47" s="12" t="s">
@@ -2657,7 +2745,9 @@
       <c r="E47" s="5"/>
       <c r="F47" s="5"/>
       <c r="G47" s="10"/>
-      <c r="H47" s="8"/>
+      <c r="H47" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="48" spans="1:8">
       <c r="A48" s="12" t="s">
@@ -2675,7 +2765,9 @@
       <c r="E48" s="5"/>
       <c r="F48" s="5"/>
       <c r="G48" s="10"/>
-      <c r="H48" s="8"/>
+      <c r="H48" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="49" spans="1:8">
       <c r="A49" s="12" t="s">
@@ -2693,7 +2785,9 @@
       <c r="E49" s="5"/>
       <c r="F49" s="5"/>
       <c r="G49" s="10"/>
-      <c r="H49" s="8"/>
+      <c r="H49" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="50" spans="1:8">
       <c r="A50" s="12" t="s">
@@ -2711,7 +2805,9 @@
       <c r="E50" s="5"/>
       <c r="F50" s="5"/>
       <c r="G50" s="10"/>
-      <c r="H50" s="8"/>
+      <c r="H50" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="51" spans="1:8">
       <c r="A51" s="12" t="s">
@@ -2729,7 +2825,9 @@
       <c r="E51" s="5"/>
       <c r="F51" s="5"/>
       <c r="G51" s="10"/>
-      <c r="H51" s="8"/>
+      <c r="H51" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="52" spans="1:8">
       <c r="A52" s="12" t="s">
@@ -2747,7 +2845,9 @@
       <c r="E52" s="5"/>
       <c r="F52" s="5"/>
       <c r="G52" s="10"/>
-      <c r="H52" s="8"/>
+      <c r="H52" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="53" spans="1:8">
       <c r="A53" s="12" t="s">
@@ -2765,7 +2865,9 @@
       <c r="E53" s="5"/>
       <c r="F53" s="5"/>
       <c r="G53" s="10"/>
-      <c r="H53" s="8"/>
+      <c r="H53" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="54" spans="1:8">
       <c r="A54" s="12" t="s">
@@ -2783,7 +2885,9 @@
       <c r="E54" s="5"/>
       <c r="F54" s="5"/>
       <c r="G54" s="10"/>
-      <c r="H54" s="8"/>
+      <c r="H54" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="55" spans="1:8">
       <c r="A55" s="12" t="s">
@@ -2801,7 +2905,9 @@
       <c r="E55" s="5"/>
       <c r="F55" s="5"/>
       <c r="G55" s="10"/>
-      <c r="H55" s="8"/>
+      <c r="H55" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="56" spans="1:8">
       <c r="A56" s="12" t="s">
@@ -2819,7 +2925,9 @@
       <c r="E56" s="5"/>
       <c r="F56" s="5"/>
       <c r="G56" s="10"/>
-      <c r="H56" s="8"/>
+      <c r="H56" s="8">
+        <v>64.285714299999995</v>
+      </c>
     </row>
     <row r="57" spans="1:8">
       <c r="A57" s="12" t="s">
@@ -2837,7 +2945,9 @@
       <c r="E57" s="5"/>
       <c r="F57" s="5"/>
       <c r="G57" s="10"/>
-      <c r="H57" s="8"/>
+      <c r="H57" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="58" spans="1:8">
       <c r="A58" s="12" t="s">
@@ -2855,7 +2965,9 @@
       <c r="E58" s="5"/>
       <c r="F58" s="5"/>
       <c r="G58" s="10"/>
-      <c r="H58" s="8"/>
+      <c r="H58" s="8">
+        <v>50</v>
+      </c>
     </row>
     <row r="59" spans="1:8">
       <c r="A59" s="12" t="s">
@@ -2873,7 +2985,9 @@
       <c r="E59" s="5"/>
       <c r="F59" s="5"/>
       <c r="G59" s="10"/>
-      <c r="H59" s="8"/>
+      <c r="H59" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="60" spans="1:8">
       <c r="A60" s="12" t="s">
@@ -2891,7 +3005,9 @@
       <c r="E60" s="5"/>
       <c r="F60" s="5"/>
       <c r="G60" s="10"/>
-      <c r="H60" s="8"/>
+      <c r="H60" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="61" spans="1:8">
       <c r="A61" s="12" t="s">
@@ -2909,7 +3025,9 @@
       <c r="E61" s="5"/>
       <c r="F61" s="5"/>
       <c r="G61" s="10"/>
-      <c r="H61" s="8"/>
+      <c r="H61" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="62" spans="1:8">
       <c r="A62" s="12" t="s">
@@ -2927,7 +3045,9 @@
       <c r="E62" s="5"/>
       <c r="F62" s="5"/>
       <c r="G62" s="10"/>
-      <c r="H62" s="8"/>
+      <c r="H62" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="63" spans="1:8">
       <c r="A63" s="12" t="s">
@@ -2945,7 +3065,9 @@
       <c r="E63" s="5"/>
       <c r="F63" s="5"/>
       <c r="G63" s="10"/>
-      <c r="H63" s="8"/>
+      <c r="H63" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="64" spans="1:8">
       <c r="A64" s="12" t="s">
@@ -2963,7 +3085,9 @@
       <c r="E64" s="5"/>
       <c r="F64" s="5"/>
       <c r="G64" s="10"/>
-      <c r="H64" s="8"/>
+      <c r="H64" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="65" spans="1:8">
       <c r="A65" s="12" t="s">
@@ -2981,7 +3105,9 @@
       <c r="E65" s="5"/>
       <c r="F65" s="5"/>
       <c r="G65" s="10"/>
-      <c r="H65" s="8"/>
+      <c r="H65" s="8">
+        <v>64.285714299999995</v>
+      </c>
     </row>
     <row r="66" spans="1:8">
       <c r="A66" s="12" t="s">
@@ -2999,7 +3125,9 @@
       <c r="E66" s="5"/>
       <c r="F66" s="5"/>
       <c r="G66" s="10"/>
-      <c r="H66" s="8"/>
+      <c r="H66" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="67" spans="1:8">
       <c r="A67" s="12" t="s">
@@ -3017,7 +3145,9 @@
       <c r="E67" s="5"/>
       <c r="F67" s="5"/>
       <c r="G67" s="10"/>
-      <c r="H67" s="8"/>
+      <c r="H67" s="8">
+        <v>64.285714299999995</v>
+      </c>
     </row>
     <row r="68" spans="1:8">
       <c r="A68" s="12" t="s">
@@ -3035,7 +3165,9 @@
       <c r="E68" s="5"/>
       <c r="F68" s="5"/>
       <c r="G68" s="10"/>
-      <c r="H68" s="8"/>
+      <c r="H68" s="8">
+        <v>53.846153799999996</v>
+      </c>
     </row>
     <row r="69" spans="1:8">
       <c r="A69" s="12" t="s">
@@ -3053,7 +3185,9 @@
       <c r="E69" s="5"/>
       <c r="F69" s="5"/>
       <c r="G69" s="10"/>
-      <c r="H69" s="8"/>
+      <c r="H69" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="70" spans="1:8">
       <c r="A70" s="12" t="s">
@@ -3071,7 +3205,9 @@
       <c r="E70" s="5"/>
       <c r="F70" s="5"/>
       <c r="G70" s="10"/>
-      <c r="H70" s="8"/>
+      <c r="H70" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="71" spans="1:8">
       <c r="A71" s="12" t="s">
@@ -3089,7 +3225,9 @@
       <c r="E71" s="5"/>
       <c r="F71" s="5"/>
       <c r="G71" s="10"/>
-      <c r="H71" s="8"/>
+      <c r="H71" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="72" spans="1:8">
       <c r="A72" s="12" t="s">
@@ -3107,7 +3245,9 @@
       <c r="E72" s="5"/>
       <c r="F72" s="5"/>
       <c r="G72" s="10"/>
-      <c r="H72" s="8"/>
+      <c r="H72" s="8">
+        <v>76.923076899999998</v>
+      </c>
     </row>
     <row r="73" spans="1:8">
       <c r="A73" s="12" t="s">
@@ -3125,7 +3265,9 @@
       <c r="E73" s="5"/>
       <c r="F73" s="5"/>
       <c r="G73" s="10"/>
-      <c r="H73" s="8"/>
+      <c r="H73" s="8">
+        <v>57.142857100000001</v>
+      </c>
     </row>
     <row r="74" spans="1:8">
       <c r="A74" s="12" t="s">
@@ -3143,7 +3285,9 @@
       <c r="E74" s="7"/>
       <c r="F74" s="5"/>
       <c r="G74" s="10"/>
-      <c r="H74" s="8"/>
+      <c r="H74" s="8">
+        <v>7.1428570999999996</v>
+      </c>
     </row>
     <row r="75" spans="1:8">
       <c r="A75" s="12" t="s">
@@ -3161,7 +3305,9 @@
       <c r="E75" s="5"/>
       <c r="F75" s="5"/>
       <c r="G75" s="10"/>
-      <c r="H75" s="8"/>
+      <c r="H75" s="8">
+        <v>64.285714299999995</v>
+      </c>
     </row>
     <row r="76" spans="1:8">
       <c r="A76" s="12" t="s">
@@ -3179,7 +3325,9 @@
       <c r="E76" s="5"/>
       <c r="F76" s="5"/>
       <c r="G76" s="10"/>
-      <c r="H76" s="8"/>
+      <c r="H76" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="77" spans="1:8">
       <c r="A77" s="12" t="s">
@@ -3197,7 +3345,9 @@
       <c r="E77" s="5"/>
       <c r="F77" s="5"/>
       <c r="G77" s="10"/>
-      <c r="H77" s="8"/>
+      <c r="H77" s="8">
+        <v>64.285714299999995</v>
+      </c>
     </row>
     <row r="78" spans="1:8">
       <c r="A78" s="12" t="s">
@@ -3215,7 +3365,9 @@
       <c r="E78" s="5"/>
       <c r="F78" s="5"/>
       <c r="G78" s="10"/>
-      <c r="H78" s="8"/>
+      <c r="H78" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="79" spans="1:8">
       <c r="A79" s="12" t="s">
@@ -3233,7 +3385,9 @@
       <c r="E79" s="5"/>
       <c r="F79" s="5"/>
       <c r="G79" s="10"/>
-      <c r="H79" s="8"/>
+      <c r="H79" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="80" spans="1:8">
       <c r="A80" s="12" t="s">
@@ -3251,7 +3405,9 @@
       <c r="E80" s="5"/>
       <c r="F80" s="5"/>
       <c r="G80" s="10"/>
-      <c r="H80" s="8"/>
+      <c r="H80" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="81" spans="1:8">
       <c r="A81" s="12" t="s">
@@ -3269,7 +3425,9 @@
       <c r="E81" s="5"/>
       <c r="F81" s="5"/>
       <c r="G81" s="10"/>
-      <c r="H81" s="8"/>
+      <c r="H81" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="82" spans="1:8">
       <c r="A82" s="12" t="s">
@@ -3287,7 +3445,9 @@
       <c r="E82" s="5"/>
       <c r="F82" s="5"/>
       <c r="G82" s="10"/>
-      <c r="H82" s="8"/>
+      <c r="H82" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="83" spans="1:8">
       <c r="A83" s="12" t="s">
@@ -3305,7 +3465,9 @@
       <c r="E83" s="5"/>
       <c r="F83" s="5"/>
       <c r="G83" s="10"/>
-      <c r="H83" s="8"/>
+      <c r="H83" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="84" spans="1:8">
       <c r="A84" s="12" t="s">
@@ -3323,7 +3485,9 @@
       <c r="E84" s="5"/>
       <c r="F84" s="5"/>
       <c r="G84" s="10"/>
-      <c r="H84" s="8"/>
+      <c r="H84" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="85" spans="1:8">
       <c r="A85" s="12" t="s">
@@ -3341,7 +3505,9 @@
       <c r="E85" s="5"/>
       <c r="F85" s="5"/>
       <c r="G85" s="10"/>
-      <c r="H85" s="8"/>
+      <c r="H85" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="86" spans="1:8">
       <c r="A86" s="12" t="s">
@@ -3359,7 +3525,9 @@
       <c r="E86" s="5"/>
       <c r="F86" s="5"/>
       <c r="G86" s="10"/>
-      <c r="H86" s="8"/>
+      <c r="H86" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="87" spans="1:8">
       <c r="A87" s="12" t="s">
@@ -3377,7 +3545,9 @@
       <c r="E87" s="5"/>
       <c r="F87" s="5"/>
       <c r="G87" s="10"/>
-      <c r="H87" s="8"/>
+      <c r="H87" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="88" spans="1:8">
       <c r="A88" s="12" t="s">
@@ -3395,7 +3565,9 @@
       <c r="E88" s="5"/>
       <c r="F88" s="5"/>
       <c r="G88" s="10"/>
-      <c r="H88" s="8"/>
+      <c r="H88" s="8">
+        <v>35.714285699999998</v>
+      </c>
     </row>
     <row r="89" spans="1:8">
       <c r="A89" s="12" t="s">
@@ -3413,7 +3585,9 @@
       <c r="E89" s="5"/>
       <c r="F89" s="5"/>
       <c r="G89" s="10"/>
-      <c r="H89" s="8"/>
+      <c r="H89" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="90" spans="1:8">
       <c r="A90" s="12" t="s">
@@ -3431,7 +3605,9 @@
       <c r="E90" s="5"/>
       <c r="F90" s="5"/>
       <c r="G90" s="10"/>
-      <c r="H90" s="8"/>
+      <c r="H90" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="91" spans="1:8">
       <c r="A91" s="12" t="s">
@@ -3449,7 +3625,9 @@
       <c r="E91" s="5"/>
       <c r="F91" s="5"/>
       <c r="G91" s="10"/>
-      <c r="H91" s="8"/>
+      <c r="H91" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="92" spans="1:8">
       <c r="A92" s="12" t="s">
@@ -3467,7 +3645,9 @@
       <c r="E92" s="5"/>
       <c r="F92" s="5"/>
       <c r="G92" s="10"/>
-      <c r="H92" s="8"/>
+      <c r="H92" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="93" spans="1:8">
       <c r="A93" s="12" t="s">
@@ -3485,7 +3665,9 @@
       <c r="E93" s="5"/>
       <c r="F93" s="5"/>
       <c r="G93" s="10"/>
-      <c r="H93" s="8"/>
+      <c r="H93" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="94" spans="1:8">
       <c r="A94" s="12" t="s">
@@ -3503,7 +3685,9 @@
       <c r="E94" s="5"/>
       <c r="F94" s="5"/>
       <c r="G94" s="10"/>
-      <c r="H94" s="8"/>
+      <c r="H94" s="8">
+        <v>50</v>
+      </c>
     </row>
     <row r="95" spans="1:8">
       <c r="A95" s="12" t="s">
@@ -3521,7 +3705,9 @@
       <c r="E95" s="5"/>
       <c r="F95" s="5"/>
       <c r="G95" s="10"/>
-      <c r="H95" s="8"/>
+      <c r="H95" s="8">
+        <v>35.714285699999998</v>
+      </c>
     </row>
     <row r="96" spans="1:8">
       <c r="A96" s="12" t="s">
@@ -3539,7 +3725,9 @@
       <c r="E96" s="5"/>
       <c r="F96" s="5"/>
       <c r="G96" s="10"/>
-      <c r="H96" s="8"/>
+      <c r="H96" s="8">
+        <v>64.285714299999995</v>
+      </c>
     </row>
     <row r="97" spans="1:8">
       <c r="A97" s="12" t="s">
@@ -3557,7 +3745,9 @@
       <c r="E97" s="5"/>
       <c r="F97" s="5"/>
       <c r="G97" s="10"/>
-      <c r="H97" s="8"/>
+      <c r="H97" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="98" spans="1:8">
       <c r="A98" s="12" t="s">
@@ -3575,7 +3765,9 @@
       <c r="E98" s="5"/>
       <c r="F98" s="5"/>
       <c r="G98" s="10"/>
-      <c r="H98" s="8"/>
+      <c r="H98" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="99" spans="1:8">
       <c r="A99" s="12" t="s">
@@ -3593,7 +3785,9 @@
       <c r="E99" s="5"/>
       <c r="F99" s="5"/>
       <c r="G99" s="10"/>
-      <c r="H99" s="8"/>
+      <c r="H99" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="100" spans="1:8">
       <c r="A100" s="11" t="s">
@@ -3611,7 +3805,9 @@
       <c r="E100" s="5"/>
       <c r="F100" s="5"/>
       <c r="G100" s="10"/>
-      <c r="H100" s="8"/>
+      <c r="H100" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="101" spans="1:8">
       <c r="A101" s="11" t="s">
@@ -3629,7 +3825,9 @@
       <c r="E101" s="5"/>
       <c r="F101" s="5"/>
       <c r="G101" s="10"/>
-      <c r="H101" s="8"/>
+      <c r="H101" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="102" spans="1:8">
       <c r="A102" s="11" t="s">
@@ -3647,7 +3845,9 @@
       <c r="E102" s="5"/>
       <c r="F102" s="5"/>
       <c r="G102" s="10"/>
-      <c r="H102" s="8"/>
+      <c r="H102" s="8">
+        <v>42.857142899999999</v>
+      </c>
     </row>
     <row r="103" spans="1:8">
       <c r="A103" s="11" t="s">
@@ -3665,7 +3865,9 @@
       <c r="E103" s="7"/>
       <c r="F103" s="5"/>
       <c r="G103" s="10"/>
-      <c r="H103" s="8"/>
+      <c r="H103" s="8">
+        <v>0</v>
+      </c>
     </row>
     <row r="104" spans="1:8">
       <c r="A104" s="11" t="s">
@@ -3683,7 +3885,9 @@
       <c r="E104" s="5"/>
       <c r="F104" s="5"/>
       <c r="G104" s="10"/>
-      <c r="H104" s="8"/>
+      <c r="H104" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="105" spans="1:8">
       <c r="A105" s="11" t="s">
@@ -3701,7 +3905,9 @@
       <c r="E105" s="5"/>
       <c r="F105" s="5"/>
       <c r="G105" s="10"/>
-      <c r="H105" s="8"/>
+      <c r="H105" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="106" spans="1:8">
       <c r="A106" s="11" t="s">
@@ -3719,7 +3925,9 @@
       <c r="E106" s="5"/>
       <c r="F106" s="5"/>
       <c r="G106" s="10"/>
-      <c r="H106" s="8"/>
+      <c r="H106" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="107" spans="1:8">
       <c r="A107" s="11" t="s">
@@ -3737,7 +3945,9 @@
       <c r="E107" s="5"/>
       <c r="F107" s="5"/>
       <c r="G107" s="10"/>
-      <c r="H107" s="8"/>
+      <c r="H107" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="108" spans="1:8">
       <c r="A108" s="11" t="s">
@@ -3755,7 +3965,9 @@
       <c r="E108" s="5"/>
       <c r="F108" s="5"/>
       <c r="G108" s="10"/>
-      <c r="H108" s="8"/>
+      <c r="H108" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="109" spans="1:8">
       <c r="A109" s="11" t="s">
@@ -3773,7 +3985,9 @@
       <c r="E109" s="5"/>
       <c r="F109" s="5"/>
       <c r="G109" s="10"/>
-      <c r="H109" s="8"/>
+      <c r="H109" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="110" spans="1:8">
       <c r="A110" s="11" t="s">
@@ -3791,7 +4005,9 @@
       <c r="E110" s="5"/>
       <c r="F110" s="5"/>
       <c r="G110" s="10"/>
-      <c r="H110" s="8"/>
+      <c r="H110" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="111" spans="1:8">
       <c r="A111" s="11" t="s">
@@ -3809,7 +4025,9 @@
       <c r="E111" s="5"/>
       <c r="F111" s="5"/>
       <c r="G111" s="10"/>
-      <c r="H111" s="8"/>
+      <c r="H111" s="8">
+        <v>57.142857100000001</v>
+      </c>
     </row>
     <row r="112" spans="1:8">
       <c r="A112" s="11" t="s">
@@ -3827,7 +4045,9 @@
       <c r="E112" s="5"/>
       <c r="F112" s="5"/>
       <c r="G112" s="10"/>
-      <c r="H112" s="8"/>
+      <c r="H112" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="113" spans="1:8">
       <c r="A113" s="11" t="s">
@@ -3845,7 +4065,9 @@
       <c r="E113" s="5"/>
       <c r="F113" s="5"/>
       <c r="G113" s="10"/>
-      <c r="H113" s="8"/>
+      <c r="H113" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="114" spans="1:8">
       <c r="A114" s="11" t="s">
@@ -3863,7 +4085,9 @@
       <c r="E114" s="5"/>
       <c r="F114" s="5"/>
       <c r="G114" s="10"/>
-      <c r="H114" s="8"/>
+      <c r="H114" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="115" spans="1:8">
       <c r="A115" s="11" t="s">
@@ -3881,7 +4105,9 @@
       <c r="E115" s="5"/>
       <c r="F115" s="5"/>
       <c r="G115" s="10"/>
-      <c r="H115" s="8"/>
+      <c r="H115" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="116" spans="1:8">
       <c r="A116" s="11" t="s">
@@ -3899,7 +4125,9 @@
       <c r="E116" s="5"/>
       <c r="F116" s="5"/>
       <c r="G116" s="10"/>
-      <c r="H116" s="8"/>
+      <c r="H116" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="117" spans="1:8">
       <c r="A117" s="11" t="s">
@@ -3917,7 +4145,9 @@
       <c r="E117" s="5"/>
       <c r="F117" s="5"/>
       <c r="G117" s="10"/>
-      <c r="H117" s="8"/>
+      <c r="H117" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="118" spans="1:8">
       <c r="A118" s="11" t="s">
@@ -3935,7 +4165,9 @@
       <c r="E118" s="5"/>
       <c r="F118" s="5"/>
       <c r="G118" s="10"/>
-      <c r="H118" s="8"/>
+      <c r="H118" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="119" spans="1:8">
       <c r="A119" s="11" t="s">
@@ -3953,7 +4185,9 @@
       <c r="E119" s="5"/>
       <c r="F119" s="5"/>
       <c r="G119" s="10"/>
-      <c r="H119" s="8"/>
+      <c r="H119" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="120" spans="1:8">
       <c r="A120" s="11" t="s">
@@ -3971,7 +4205,9 @@
       <c r="E120" s="5"/>
       <c r="F120" s="5"/>
       <c r="G120" s="10"/>
-      <c r="H120" s="8"/>
+      <c r="H120" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="121" spans="1:8">
       <c r="A121" s="11" t="s">
@@ -3989,7 +4225,9 @@
       <c r="E121" s="5"/>
       <c r="F121" s="5"/>
       <c r="G121" s="10"/>
-      <c r="H121" s="8"/>
+      <c r="H121" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="122" spans="1:8">
       <c r="A122" s="11" t="s">
@@ -4007,7 +4245,9 @@
       <c r="E122" s="5"/>
       <c r="F122" s="5"/>
       <c r="G122" s="10"/>
-      <c r="H122" s="8"/>
+      <c r="H122" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="123" spans="1:8">
       <c r="A123" s="11" t="s">
@@ -4025,7 +4265,9 @@
       <c r="E123" s="5"/>
       <c r="F123" s="5"/>
       <c r="G123" s="10"/>
-      <c r="H123" s="8"/>
+      <c r="H123" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="124" spans="1:8">
       <c r="A124" s="11" t="s">
@@ -4043,7 +4285,9 @@
       <c r="E124" s="5"/>
       <c r="F124" s="5"/>
       <c r="G124" s="10"/>
-      <c r="H124" s="8"/>
+      <c r="H124" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="125" spans="1:8">
       <c r="A125" s="11" t="s">
@@ -4061,7 +4305,9 @@
       <c r="E125" s="5"/>
       <c r="F125" s="5"/>
       <c r="G125" s="10"/>
-      <c r="H125" s="8"/>
+      <c r="H125" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="126" spans="1:8">
       <c r="A126" s="11" t="s">
@@ -4079,7 +4325,9 @@
       <c r="E126" s="5"/>
       <c r="F126" s="5"/>
       <c r="G126" s="10"/>
-      <c r="H126" s="8"/>
+      <c r="H126" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="127" spans="1:8">
       <c r="A127" s="11" t="s">
@@ -4097,7 +4345,9 @@
       <c r="E127" s="5"/>
       <c r="F127" s="5"/>
       <c r="G127" s="10"/>
-      <c r="H127" s="8"/>
+      <c r="H127" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="128" spans="1:8">
       <c r="A128" s="11" t="s">
@@ -4115,7 +4365,9 @@
       <c r="E128" s="5"/>
       <c r="F128" s="5"/>
       <c r="G128" s="10"/>
-      <c r="H128" s="8"/>
+      <c r="H128" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="129" spans="1:8">
       <c r="A129" s="11" t="s">
@@ -4133,7 +4385,9 @@
       <c r="E129" s="5"/>
       <c r="F129" s="5"/>
       <c r="G129" s="10"/>
-      <c r="H129" s="8"/>
+      <c r="H129" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="130" spans="1:8">
       <c r="A130" s="11" t="s">
@@ -4151,7 +4405,9 @@
       <c r="E130" s="5"/>
       <c r="F130" s="5"/>
       <c r="G130" s="10"/>
-      <c r="H130" s="8"/>
+      <c r="H130" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="131" spans="1:8">
       <c r="A131" s="11" t="s">
@@ -4169,7 +4425,9 @@
       <c r="E131" s="5"/>
       <c r="F131" s="5"/>
       <c r="G131" s="10"/>
-      <c r="H131" s="8"/>
+      <c r="H131" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="132" spans="1:8">
       <c r="A132" s="11" t="s">
@@ -4187,7 +4445,9 @@
       <c r="E132" s="5"/>
       <c r="F132" s="5"/>
       <c r="G132" s="10"/>
-      <c r="H132" s="8"/>
+      <c r="H132" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="133" spans="1:8">
       <c r="A133" s="11" t="s">
@@ -4205,7 +4465,9 @@
       <c r="E133" s="5"/>
       <c r="F133" s="5"/>
       <c r="G133" s="10"/>
-      <c r="H133" s="8"/>
+      <c r="H133" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="134" spans="1:8">
       <c r="A134" s="11" t="s">
@@ -4223,7 +4485,9 @@
       <c r="E134" s="5"/>
       <c r="F134" s="5"/>
       <c r="G134" s="10"/>
-      <c r="H134" s="8"/>
+      <c r="H134" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="135" spans="1:8">
       <c r="A135" s="11" t="s">
@@ -4241,7 +4505,9 @@
       <c r="E135" s="5"/>
       <c r="F135" s="5"/>
       <c r="G135" s="10"/>
-      <c r="H135" s="8"/>
+      <c r="H135" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="136" spans="1:8">
       <c r="A136" s="11" t="s">
@@ -4259,7 +4525,9 @@
       <c r="E136" s="5"/>
       <c r="F136" s="5"/>
       <c r="G136" s="10"/>
-      <c r="H136" s="8"/>
+      <c r="H136" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="137" spans="1:8">
       <c r="A137" s="11" t="s">
@@ -4277,7 +4545,9 @@
       <c r="E137" s="5"/>
       <c r="F137" s="5"/>
       <c r="G137" s="10"/>
-      <c r="H137" s="8"/>
+      <c r="H137" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="138" spans="1:8">
       <c r="A138" s="11" t="s">
@@ -4295,7 +4565,9 @@
       <c r="E138" s="5"/>
       <c r="F138" s="5"/>
       <c r="G138" s="10"/>
-      <c r="H138" s="8"/>
+      <c r="H138" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="139" spans="1:8">
       <c r="A139" s="11" t="s">
@@ -4313,7 +4585,9 @@
       <c r="E139" s="5"/>
       <c r="F139" s="5"/>
       <c r="G139" s="10"/>
-      <c r="H139" s="8"/>
+      <c r="H139" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="140" spans="1:8">
       <c r="A140" s="11" t="s">
@@ -4331,7 +4605,9 @@
       <c r="E140" s="5"/>
       <c r="F140" s="5"/>
       <c r="G140" s="10"/>
-      <c r="H140" s="8"/>
+      <c r="H140" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="141" spans="1:8">
       <c r="A141" s="11" t="s">
@@ -4349,7 +4625,9 @@
       <c r="E141" s="5"/>
       <c r="F141" s="5"/>
       <c r="G141" s="10"/>
-      <c r="H141" s="8"/>
+      <c r="H141" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="142" spans="1:8">
       <c r="A142" s="11" t="s">
@@ -4367,7 +4645,9 @@
       <c r="E142" s="5"/>
       <c r="F142" s="5"/>
       <c r="G142" s="10"/>
-      <c r="H142" s="8"/>
+      <c r="H142" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="143" spans="1:8">
       <c r="A143" s="11" t="s">
@@ -4385,7 +4665,9 @@
       <c r="E143" s="5"/>
       <c r="F143" s="5"/>
       <c r="G143" s="10"/>
-      <c r="H143" s="8"/>
+      <c r="H143" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="144" spans="1:8">
       <c r="A144" s="11" t="s">
@@ -4403,7 +4685,9 @@
       <c r="E144" s="5"/>
       <c r="F144" s="5"/>
       <c r="G144" s="10"/>
-      <c r="H144" s="8"/>
+      <c r="H144" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="145" spans="1:8">
       <c r="A145" s="11" t="s">
@@ -4421,7 +4705,9 @@
       <c r="E145" s="5"/>
       <c r="F145" s="5"/>
       <c r="G145" s="10"/>
-      <c r="H145" s="8"/>
+      <c r="H145" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="146" spans="1:8">
       <c r="A146" s="11" t="s">
@@ -4439,7 +4725,9 @@
       <c r="E146" s="5"/>
       <c r="F146" s="5"/>
       <c r="G146" s="10"/>
-      <c r="H146" s="8"/>
+      <c r="H146" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="147" spans="1:8">
       <c r="A147" s="11" t="s">
@@ -4457,7 +4745,9 @@
       <c r="E147" s="5"/>
       <c r="F147" s="5"/>
       <c r="G147" s="10"/>
-      <c r="H147" s="8"/>
+      <c r="H147" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="148" spans="1:8">
       <c r="A148" s="11" t="s">
@@ -4475,7 +4765,9 @@
       <c r="E148" s="5"/>
       <c r="F148" s="5"/>
       <c r="G148" s="10"/>
-      <c r="H148" s="8"/>
+      <c r="H148" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="149" spans="1:8">
       <c r="A149" s="11" t="s">
@@ -4493,7 +4785,9 @@
       <c r="E149" s="5"/>
       <c r="F149" s="5"/>
       <c r="G149" s="10"/>
-      <c r="H149" s="8"/>
+      <c r="H149" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="150" spans="1:8">
       <c r="A150" s="11" t="s">
@@ -4511,7 +4805,9 @@
       <c r="E150" s="5"/>
       <c r="F150" s="5"/>
       <c r="G150" s="10"/>
-      <c r="H150" s="8"/>
+      <c r="H150" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="151" spans="1:8">
       <c r="A151" s="11" t="s">
@@ -4529,7 +4825,9 @@
       <c r="E151" s="5"/>
       <c r="F151" s="5"/>
       <c r="G151" s="10"/>
-      <c r="H151" s="8"/>
+      <c r="H151" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="152" spans="1:8">
       <c r="A152" s="11" t="s">
@@ -4547,7 +4845,9 @@
       <c r="E152" s="5"/>
       <c r="F152" s="5"/>
       <c r="G152" s="10"/>
-      <c r="H152" s="8"/>
+      <c r="H152" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="153" spans="1:8">
       <c r="A153" s="11" t="s">
@@ -4565,7 +4865,9 @@
       <c r="E153" s="5"/>
       <c r="F153" s="5"/>
       <c r="G153" s="10"/>
-      <c r="H153" s="8"/>
+      <c r="H153" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="154" spans="1:8">
       <c r="A154" s="11" t="s">
@@ -4583,7 +4885,9 @@
       <c r="E154" s="5"/>
       <c r="F154" s="5"/>
       <c r="G154" s="10"/>
-      <c r="H154" s="8"/>
+      <c r="H154" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="155" spans="1:8">
       <c r="A155" s="11" t="s">
@@ -4601,7 +4905,9 @@
       <c r="E155" s="5"/>
       <c r="F155" s="5"/>
       <c r="G155" s="10"/>
-      <c r="H155" s="8"/>
+      <c r="H155" s="8">
+        <v>64.285714299999995</v>
+      </c>
     </row>
     <row r="156" spans="1:8">
       <c r="A156" s="11" t="s">
@@ -4619,7 +4925,9 @@
       <c r="E156" s="5"/>
       <c r="F156" s="5"/>
       <c r="G156" s="10"/>
-      <c r="H156" s="8"/>
+      <c r="H156" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="157" spans="1:8">
       <c r="A157" s="11" t="s">
@@ -4637,7 +4945,9 @@
       <c r="E157" s="5"/>
       <c r="F157" s="5"/>
       <c r="G157" s="10"/>
-      <c r="H157" s="8"/>
+      <c r="H157" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="158" spans="1:8">
       <c r="A158" s="11" t="s">
@@ -4655,7 +4965,9 @@
       <c r="E158" s="5"/>
       <c r="F158" s="5"/>
       <c r="G158" s="10"/>
-      <c r="H158" s="8"/>
+      <c r="H158" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="159" spans="1:8">
       <c r="A159" s="11" t="s">
@@ -4673,7 +4985,9 @@
       <c r="E159" s="5"/>
       <c r="F159" s="5"/>
       <c r="G159" s="10"/>
-      <c r="H159" s="8"/>
+      <c r="H159" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="160" spans="1:8">
       <c r="A160" s="11" t="s">
@@ -4691,7 +5005,9 @@
       <c r="E160" s="5"/>
       <c r="F160" s="5"/>
       <c r="G160" s="10"/>
-      <c r="H160" s="8"/>
+      <c r="H160" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="161" spans="1:8">
       <c r="A161" s="11" t="s">
@@ -4709,7 +5025,9 @@
       <c r="E161" s="5"/>
       <c r="F161" s="5"/>
       <c r="G161" s="10"/>
-      <c r="H161" s="8"/>
+      <c r="H161" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="162" spans="1:8">
       <c r="A162" s="11" t="s">
@@ -4727,7 +5045,9 @@
       <c r="E162" s="5"/>
       <c r="F162" s="5"/>
       <c r="G162" s="10"/>
-      <c r="H162" s="8"/>
+      <c r="H162" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="163" spans="1:8">
       <c r="A163" s="11" t="s">
@@ -4745,7 +5065,9 @@
       <c r="E163" s="5"/>
       <c r="F163" s="5"/>
       <c r="G163" s="10"/>
-      <c r="H163" s="8"/>
+      <c r="H163" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="164" spans="1:8">
       <c r="A164" s="11" t="s">
@@ -4763,7 +5085,9 @@
       <c r="E164" s="5"/>
       <c r="F164" s="5"/>
       <c r="G164" s="10"/>
-      <c r="H164" s="8"/>
+      <c r="H164" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="165" spans="1:8">
       <c r="A165" s="11" t="s">
@@ -4781,7 +5105,9 @@
       <c r="E165" s="5"/>
       <c r="F165" s="5"/>
       <c r="G165" s="10"/>
-      <c r="H165" s="8"/>
+      <c r="H165" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="166" spans="1:8">
       <c r="A166" s="11" t="s">
@@ -4799,7 +5125,9 @@
       <c r="E166" s="5"/>
       <c r="F166" s="5"/>
       <c r="G166" s="10"/>
-      <c r="H166" s="8"/>
+      <c r="H166" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="167" spans="1:8">
       <c r="A167" s="11" t="s">
@@ -4817,7 +5145,9 @@
       <c r="E167" s="5"/>
       <c r="F167" s="5"/>
       <c r="G167" s="10"/>
-      <c r="H167" s="8"/>
+      <c r="H167" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="168" spans="1:8">
       <c r="A168" s="11" t="s">
@@ -4835,7 +5165,9 @@
       <c r="E168" s="5"/>
       <c r="F168" s="5"/>
       <c r="G168" s="10"/>
-      <c r="H168" s="8"/>
+      <c r="H168" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="169" spans="1:8">
       <c r="A169" s="11" t="s">
@@ -4853,7 +5185,9 @@
       <c r="E169" s="5"/>
       <c r="F169" s="5"/>
       <c r="G169" s="10"/>
-      <c r="H169" s="8"/>
+      <c r="H169" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="170" spans="1:8">
       <c r="A170" s="11" t="s">
@@ -4871,7 +5205,9 @@
       <c r="E170" s="5"/>
       <c r="F170" s="5"/>
       <c r="G170" s="10"/>
-      <c r="H170" s="8"/>
+      <c r="H170" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="171" spans="1:8">
       <c r="A171" s="11" t="s">
@@ -4889,7 +5225,9 @@
       <c r="E171" s="5"/>
       <c r="F171" s="5"/>
       <c r="G171" s="10"/>
-      <c r="H171" s="8"/>
+      <c r="H171" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="172" spans="1:8">
       <c r="A172" s="11" t="s">
@@ -4907,7 +5245,9 @@
       <c r="E172" s="5"/>
       <c r="F172" s="5"/>
       <c r="G172" s="10"/>
-      <c r="H172" s="8"/>
+      <c r="H172" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="173" spans="1:8">
       <c r="A173" s="11" t="s">
@@ -4925,7 +5265,9 @@
       <c r="E173" s="5"/>
       <c r="F173" s="5"/>
       <c r="G173" s="10"/>
-      <c r="H173" s="8"/>
+      <c r="H173" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="174" spans="1:8">
       <c r="A174" s="11" t="s">
@@ -4943,7 +5285,9 @@
       <c r="E174" s="5"/>
       <c r="F174" s="5"/>
       <c r="G174" s="10"/>
-      <c r="H174" s="8"/>
+      <c r="H174" s="8">
+        <v>76.923076899999998</v>
+      </c>
     </row>
     <row r="175" spans="1:8">
       <c r="A175" s="11" t="s">
@@ -4961,7 +5305,9 @@
       <c r="E175" s="5"/>
       <c r="F175" s="5"/>
       <c r="G175" s="10"/>
-      <c r="H175" s="8"/>
+      <c r="H175" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="176" spans="1:8">
       <c r="A176" s="11" t="s">
@@ -4979,7 +5325,9 @@
       <c r="E176" s="5"/>
       <c r="F176" s="5"/>
       <c r="G176" s="10"/>
-      <c r="H176" s="8"/>
+      <c r="H176" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="177" spans="1:8">
       <c r="A177" s="11" t="s">
@@ -4997,7 +5345,9 @@
       <c r="E177" s="5"/>
       <c r="F177" s="5"/>
       <c r="G177" s="10"/>
-      <c r="H177" s="8"/>
+      <c r="H177" s="8">
+        <v>71.428571399999996</v>
+      </c>
     </row>
     <row r="178" spans="1:8">
       <c r="A178" s="11" t="s">
@@ -5015,7 +5365,9 @@
       <c r="E178" s="5"/>
       <c r="F178" s="5"/>
       <c r="G178" s="10"/>
-      <c r="H178" s="8"/>
+      <c r="H178" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="179" spans="1:8">
       <c r="A179" s="11" t="s">
@@ -5033,7 +5385,9 @@
       <c r="E179" s="5"/>
       <c r="F179" s="5"/>
       <c r="G179" s="10"/>
-      <c r="H179" s="8"/>
+      <c r="H179" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="180" spans="1:8">
       <c r="A180" s="11" t="s">
@@ -5051,7 +5405,9 @@
       <c r="E180" s="5"/>
       <c r="F180" s="5"/>
       <c r="G180" s="10"/>
-      <c r="H180" s="8"/>
+      <c r="H180" s="8">
+        <v>78.571428600000004</v>
+      </c>
     </row>
     <row r="181" spans="1:8">
       <c r="A181" s="11" t="s">
@@ -5069,7 +5425,9 @@
       <c r="E181" s="5"/>
       <c r="F181" s="5"/>
       <c r="G181" s="10"/>
-      <c r="H181" s="8"/>
+      <c r="H181" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="182" spans="1:8">
       <c r="A182" s="11" t="s">
@@ -5087,7 +5445,9 @@
       <c r="E182" s="5"/>
       <c r="F182" s="5"/>
       <c r="G182" s="10"/>
-      <c r="H182" s="8"/>
+      <c r="H182" s="8">
+        <v>64.285714299999995</v>
+      </c>
     </row>
     <row r="183" spans="1:8">
       <c r="A183" s="11" t="s">
@@ -5105,7 +5465,9 @@
       <c r="E183" s="5"/>
       <c r="F183" s="5"/>
       <c r="G183" s="10"/>
-      <c r="H183" s="8"/>
+      <c r="H183" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="184" spans="1:8">
       <c r="A184" s="11" t="s">
@@ -5123,7 +5485,9 @@
       <c r="E184" s="5"/>
       <c r="F184" s="5"/>
       <c r="G184" s="10"/>
-      <c r="H184" s="8"/>
+      <c r="H184" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="185" spans="1:8">
       <c r="A185" s="11" t="s">
@@ -5141,7 +5505,9 @@
       <c r="E185" s="5"/>
       <c r="F185" s="5"/>
       <c r="G185" s="10"/>
-      <c r="H185" s="8"/>
+      <c r="H185" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="186" spans="1:8">
       <c r="A186" s="11" t="s">
@@ -5159,7 +5525,9 @@
       <c r="E186" s="5"/>
       <c r="F186" s="5"/>
       <c r="G186" s="10"/>
-      <c r="H186" s="8"/>
+      <c r="H186" s="8">
+        <v>100</v>
+      </c>
     </row>
     <row r="187" spans="1:8">
       <c r="A187" s="11" t="s">
@@ -5177,7 +5545,9 @@
       <c r="E187" s="5"/>
       <c r="F187" s="5"/>
       <c r="G187" s="10"/>
-      <c r="H187" s="8"/>
+      <c r="H187" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="188" spans="1:8">
       <c r="A188" s="11" t="s">
@@ -5195,7 +5565,9 @@
       <c r="E188" s="5"/>
       <c r="F188" s="5"/>
       <c r="G188" s="10"/>
-      <c r="H188" s="8"/>
+      <c r="H188" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="189" spans="1:8">
       <c r="A189" s="11" t="s">
@@ -5213,7 +5585,9 @@
       <c r="E189" s="5"/>
       <c r="F189" s="5"/>
       <c r="G189" s="10"/>
-      <c r="H189" s="8"/>
+      <c r="H189" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="190" spans="1:8">
       <c r="A190" s="11" t="s">
@@ -5231,7 +5605,9 @@
       <c r="E190" s="5"/>
       <c r="F190" s="5"/>
       <c r="G190" s="10"/>
-      <c r="H190" s="8"/>
+      <c r="H190" s="8">
+        <v>85.714285700000005</v>
+      </c>
     </row>
     <row r="191" spans="1:8">
       <c r="A191" s="11" t="s">
@@ -5249,7 +5625,9 @@
       <c r="E191" s="5"/>
       <c r="F191" s="5"/>
       <c r="G191" s="10"/>
-      <c r="H191" s="8"/>
+      <c r="H191" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="192" spans="1:8">
       <c r="A192" s="11" t="s">
@@ -5267,7 +5645,9 @@
       <c r="E192" s="5"/>
       <c r="F192" s="5"/>
       <c r="G192" s="10"/>
-      <c r="H192" s="8"/>
+      <c r="H192" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="193" spans="1:8">
       <c r="A193" s="11" t="s">
@@ -5285,7 +5665,9 @@
       <c r="E193" s="5"/>
       <c r="F193" s="5"/>
       <c r="G193" s="10"/>
-      <c r="H193" s="8"/>
+      <c r="H193" s="8">
+        <v>92.857142899999999</v>
+      </c>
     </row>
     <row r="194" spans="1:8">
       <c r="A194" s="13" t="s">
@@ -5752,9 +6134,12 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
-  <documentManagement/>
-</p:properties>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
 </file>
 
 <file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
@@ -5902,15 +6287,24 @@
 </file>
 
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement/>
+</p:properties>
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+  <ds:schemaRefs/>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
 <ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{4B92832D-94CC-4C5E-A4E8-2D2A44869573}">
   <ds:schemaRefs>
     <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
@@ -5924,16 +6318,4 @@
     <ds:schemaRef ds:uri="http://purl.org/dc/dcmitype/"/>
   </ds:schemaRefs>
 </ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
-</file>
-
-<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
-  <ds:schemaRefs/>
-</ds:datastoreItem>
 </file>
--- a/MC2020_E25.xlsx
+++ b/MC2020_E25.xlsx
@@ -5,11 +5,11 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\maids.jfn\Documents\GitHub\MC3020_Attendance\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\thuvaragan\Downloads\"/>
     </mc:Choice>
   </mc:AlternateContent>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15720"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28800" windowHeight="12180"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -30,7 +30,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="409" uniqueCount="395">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="427" uniqueCount="407">
   <si>
     <t xml:space="preserve"> Reg.number</t>
   </si>
@@ -1215,12 +1215,48 @@
   </si>
   <si>
     <t>HEWAGE H.E.S.R</t>
+  </si>
+  <si>
+    <t>2024/E/010</t>
+  </si>
+  <si>
+    <t>CHANDRARATHNA A.H.N.L.</t>
+  </si>
+  <si>
+    <t>2024/E/110</t>
+  </si>
+  <si>
+    <t>2024/E/115</t>
+  </si>
+  <si>
+    <t>SOORIYAARACHCHI S.T.</t>
+  </si>
+  <si>
+    <t>2024/E/121</t>
+  </si>
+  <si>
+    <t>NILANJANA S.M.I.M.</t>
+  </si>
+  <si>
+    <t>2024/E/184</t>
+  </si>
+  <si>
+    <t>BAWANEKE A.H.M.P.</t>
+  </si>
+  <si>
+    <t>2023/E/085</t>
+  </si>
+  <si>
+    <t>2023/E/187</t>
+  </si>
+  <si>
+    <t>PETERSON N.S.</t>
   </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" mc:Ignorable="x14ac">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" mc:Ignorable="x14ac x16r2">
   <numFmts count="1">
     <numFmt numFmtId="43" formatCode="_-* #,##0.00_-;\-* #,##0.00_-;_-* &quot;-&quot;??_-;_-@_-"/>
   </numFmts>
@@ -1417,7 +1453,7 @@
     <xf numFmtId="43" fontId="7" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="35">
+  <cellXfs count="36">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="43" fontId="0" fillId="0" borderId="0" xfId="10" applyFont="1"/>
     <xf numFmtId="0" fontId="2" fillId="9" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
@@ -1505,6 +1541,9 @@
     </xf>
     <xf numFmtId="0" fontId="11" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="49" fontId="8" fillId="0" borderId="1" xfId="0" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
     </xf>
   </cellXfs>
@@ -5688,74 +5727,126 @@
       <c r="H194" s="6"/>
     </row>
     <row r="195" spans="1:8">
-      <c r="A195" s="14"/>
-      <c r="B195" s="15"/>
-      <c r="C195" s="16"/>
-      <c r="D195" s="17"/>
-      <c r="E195" s="18"/>
-      <c r="F195" s="18"/>
-      <c r="G195" s="19"/>
-      <c r="H195" s="20"/>
+      <c r="A195" s="35" t="s">
+        <v>395</v>
+      </c>
+      <c r="B195" s="29" t="s">
+        <v>396</v>
+      </c>
+      <c r="C195" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="D195" s="10">
+        <v>79</v>
+      </c>
+      <c r="E195" s="5"/>
+      <c r="F195" s="5"/>
+      <c r="G195" s="10"/>
+      <c r="H195" s="6"/>
     </row>
     <row r="196" spans="1:8">
-      <c r="A196" s="14"/>
-      <c r="B196" s="15"/>
-      <c r="C196" s="16"/>
-      <c r="D196" s="17"/>
-      <c r="E196" s="18"/>
-      <c r="F196" s="18"/>
-      <c r="G196" s="19"/>
-      <c r="H196" s="20"/>
+      <c r="A196" s="35" t="s">
+        <v>397</v>
+      </c>
+      <c r="B196" s="29"/>
+      <c r="C196" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="D196" s="9">
+        <v>86.5</v>
+      </c>
+      <c r="E196" s="5"/>
+      <c r="F196" s="5"/>
+      <c r="G196" s="10"/>
+      <c r="H196" s="6"/>
     </row>
     <row r="197" spans="1:8">
-      <c r="A197" s="14"/>
-      <c r="B197" s="15"/>
-      <c r="C197" s="16"/>
-      <c r="D197" s="17"/>
-      <c r="E197" s="18"/>
-      <c r="F197" s="18"/>
-      <c r="G197" s="19"/>
-      <c r="H197" s="20"/>
+      <c r="A197" s="35" t="s">
+        <v>398</v>
+      </c>
+      <c r="B197" s="29" t="s">
+        <v>399</v>
+      </c>
+      <c r="C197" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="D197" s="10">
+        <v>91</v>
+      </c>
+      <c r="E197" s="5"/>
+      <c r="F197" s="5"/>
+      <c r="G197" s="10"/>
+      <c r="H197" s="6"/>
     </row>
     <row r="198" spans="1:8">
-      <c r="A198" s="14"/>
-      <c r="B198" s="15"/>
-      <c r="C198" s="16"/>
-      <c r="D198" s="17"/>
-      <c r="E198" s="18"/>
-      <c r="F198" s="18"/>
-      <c r="G198" s="19"/>
-      <c r="H198" s="20"/>
+      <c r="A198" s="35" t="s">
+        <v>400</v>
+      </c>
+      <c r="B198" s="29" t="s">
+        <v>401</v>
+      </c>
+      <c r="C198" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="D198" s="9">
+        <v>86.5</v>
+      </c>
+      <c r="E198" s="5"/>
+      <c r="F198" s="5"/>
+      <c r="G198" s="10"/>
+      <c r="H198" s="6"/>
     </row>
     <row r="199" spans="1:8">
-      <c r="A199" s="14"/>
-      <c r="B199" s="15"/>
-      <c r="C199" s="16"/>
-      <c r="D199" s="17"/>
-      <c r="E199" s="18"/>
-      <c r="F199" s="18"/>
-      <c r="G199" s="19"/>
-      <c r="H199" s="20"/>
+      <c r="A199" s="35" t="s">
+        <v>402</v>
+      </c>
+      <c r="B199" s="29" t="s">
+        <v>403</v>
+      </c>
+      <c r="C199" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="D199" s="9">
+        <v>86.5</v>
+      </c>
+      <c r="E199" s="5"/>
+      <c r="F199" s="5"/>
+      <c r="G199" s="10"/>
+      <c r="H199" s="6"/>
     </row>
     <row r="200" spans="1:8">
-      <c r="A200" s="14"/>
-      <c r="B200" s="15"/>
-      <c r="C200" s="16"/>
-      <c r="D200" s="17"/>
-      <c r="E200" s="18"/>
-      <c r="F200" s="18"/>
-      <c r="G200" s="19"/>
-      <c r="H200" s="20"/>
+      <c r="A200" s="13" t="s">
+        <v>404</v>
+      </c>
+      <c r="B200" s="31"/>
+      <c r="C200" s="10">
+        <v>36</v>
+      </c>
+      <c r="D200" s="9">
+        <v>92.5</v>
+      </c>
+      <c r="E200" s="5"/>
+      <c r="F200" s="5"/>
+      <c r="G200" s="10"/>
+      <c r="H200" s="6"/>
     </row>
     <row r="201" spans="1:8">
-      <c r="A201" s="14"/>
-      <c r="B201" s="15"/>
-      <c r="C201" s="16"/>
-      <c r="D201" s="17"/>
-      <c r="E201" s="18"/>
-      <c r="F201" s="18"/>
-      <c r="G201" s="19"/>
-      <c r="H201" s="20"/>
+      <c r="A201" s="13" t="s">
+        <v>405</v>
+      </c>
+      <c r="B201" s="31" t="s">
+        <v>406</v>
+      </c>
+      <c r="C201" s="10" t="s">
+        <v>383</v>
+      </c>
+      <c r="D201" s="9">
+        <v>86.5</v>
+      </c>
+      <c r="E201" s="5"/>
+      <c r="F201" s="5"/>
+      <c r="G201" s="10"/>
+      <c r="H201" s="6"/>
     </row>
     <row r="202" spans="1:8">
       <c r="A202" s="14"/>
@@ -6134,15 +6225,6 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
 <ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x010100FDB710AC8133AA498CBE2CD8804BFA17" ma:contentTypeVersion="4" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="4eb3d0237cfa0d187f5d6a045860a182">
   <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="a5132194-61b6-4507-86ae-3af00c68c385" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="53ffbac00c82fc65a20b2fe1c6581f58" ns2:_="">
     <xsd:import namespace="a5132194-61b6-4507-86ae-3af00c68c385"/>
@@ -6286,6 +6368,15 @@
 </ct:contentTypeSchema>
 </file>
 
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
 <file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
 <p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
   <documentManagement/>
@@ -6293,13 +6384,13 @@
 </file>
 
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F334BD5B-9873-472F-B0A9-4AE19CD21D29}">
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{82FD49CE-D196-4C00-BC5E-382EDDDD004F}">
   <ds:schemaRefs/>
 </ds:datastoreItem>
 </file>
